--- a/РАБОЧИЙ СТОЛ/расчеты ПОКОМ КИ/машины ПОКОМ КИ.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты ПОКОМ КИ/машины ПОКОМ КИ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20B8985C-BC7D-4F74-AAC3-9813411A60FD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B1F3B18-20B9-4113-A41B-FE2F32F3625C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1560,13 +1560,11 @@
         <v>30</v>
       </c>
       <c r="B21">
-        <v>1200</v>
+        <f>1200+250</f>
+        <v>1450</v>
       </c>
       <c r="D21">
         <v>3</v>
-      </c>
-      <c r="E21">
-        <v>150</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.25">
@@ -1574,13 +1572,11 @@
         <v>31</v>
       </c>
       <c r="B22">
-        <v>800</v>
+        <f>800+174</f>
+        <v>974</v>
       </c>
       <c r="D22">
         <v>2</v>
-      </c>
-      <c r="E22">
-        <v>150</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.25">
@@ -1588,13 +1584,11 @@
         <v>32</v>
       </c>
       <c r="B23">
-        <v>1000</v>
+        <f>1000+252</f>
+        <v>1252</v>
       </c>
       <c r="D23">
-        <v>2</v>
-      </c>
-      <c r="E23">
-        <v>230</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/РАБОЧИЙ СТОЛ/расчеты ПОКОМ КИ/машины ПОКОМ КИ.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчеты ПОКОМ КИ/машины ПОКОМ КИ.xlsx
@@ -1,37 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\расчеты ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B1F3B18-20B9-4113-A41B-FE2F32F3625C}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45CC25EE-7A7E-4C6A-9E01-1D652DD4DAB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="35">
   <si>
     <t>Бердянск</t>
   </si>
@@ -51,9 +45,6 @@
     <t>ПОЛУЧАТЕЛЬ</t>
   </si>
   <si>
-    <t>3 машина</t>
-  </si>
-  <si>
     <t>Остаток</t>
   </si>
   <si>
@@ -81,9 +72,6 @@
     <t>Бейдерман</t>
   </si>
   <si>
-    <t>4 машина</t>
-  </si>
-  <si>
     <t>Малахутин</t>
   </si>
   <si>
@@ -114,12 +102,6 @@
     <t>Обрыньба</t>
   </si>
   <si>
-    <t>1 машина на 27,06</t>
-  </si>
-  <si>
-    <t>1 машина на 26,06</t>
-  </si>
-  <si>
     <t>Логистон (ПРС)</t>
   </si>
   <si>
@@ -130,6 +112,24 @@
   </si>
   <si>
     <t>Бердянск сыры</t>
+  </si>
+  <si>
+    <t>1 машина на 29,06</t>
+  </si>
+  <si>
+    <t>2 машина на 29,06</t>
+  </si>
+  <si>
+    <t>3 машина на 29,06</t>
+  </si>
+  <si>
+    <t>4 машина на 29,06</t>
+  </si>
+  <si>
+    <t>1 машина на 30,06</t>
+  </si>
+  <si>
+    <t>2 машина на 30,06</t>
   </si>
 </sst>
 </file>
@@ -160,7 +160,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -173,6 +173,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="34">
     <border>
@@ -623,7 +635,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -650,24 +662,19 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -972,7 +979,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:W25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.7109375" bestFit="1" customWidth="1"/>
@@ -987,101 +994,135 @@
     <col min="13" max="13" width="6" customWidth="1"/>
     <col min="14" max="15" width="7.28515625" customWidth="1"/>
     <col min="16" max="16" width="6" customWidth="1"/>
-    <col min="17" max="17" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="7.28515625" customWidth="1"/>
+    <col min="19" max="19" width="6" customWidth="1"/>
+    <col min="20" max="21" width="7.28515625" customWidth="1"/>
+    <col min="22" max="22" width="6" customWidth="1"/>
+    <col min="23" max="23" width="8.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
+    <row r="1" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="37" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="37" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="C1" s="42" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="42" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="F1" s="44"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="44"/>
-      <c r="J1" s="45"/>
-      <c r="K1" s="40" t="s">
+      <c r="E1" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" s="39"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="I1" s="39"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="L1" s="39"/>
+      <c r="M1" s="40"/>
+      <c r="N1" s="35" t="s">
+        <v>32</v>
+      </c>
+      <c r="O1" s="39"/>
+      <c r="P1" s="40"/>
+      <c r="Q1" s="35" t="s">
+        <v>33</v>
+      </c>
+      <c r="R1" s="39"/>
+      <c r="S1" s="40"/>
+      <c r="T1" s="35" t="s">
+        <v>34</v>
+      </c>
+      <c r="U1" s="39"/>
+      <c r="V1" s="40"/>
+      <c r="W1" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="44"/>
-      <c r="M1" s="45"/>
-      <c r="N1" s="40" t="s">
-        <v>16</v>
-      </c>
-      <c r="O1" s="44"/>
-      <c r="P1" s="45"/>
-      <c r="Q1" s="38" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="41"/>
-      <c r="B2" s="43"/>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
+    </row>
+    <row r="2" spans="1:23" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="36"/>
+      <c r="B2" s="38"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
       <c r="E2" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="18" t="s">
+      <c r="G2" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="19" t="s">
-        <v>13</v>
-      </c>
       <c r="H2" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="I2" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="18" t="s">
+      <c r="J2" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="J2" s="19" t="s">
-        <v>13</v>
-      </c>
       <c r="K2" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="L2" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="18" t="s">
+      <c r="M2" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="19" t="s">
-        <v>13</v>
-      </c>
       <c r="N2" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="O2" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="O2" s="18" t="s">
+      <c r="P2" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="P2" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q2" s="39"/>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q2" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="R2" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="S2" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="T2" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="U2" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="V2" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="W2" s="34"/>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="20">
-        <v>11798</v>
+        <v>14476</v>
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="24"/>
+      <c r="E3" s="6">
+        <v>14476</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="7"/>
       <c r="H3" s="6"/>
       <c r="I3" s="3"/>
       <c r="J3" s="7"/>
@@ -1091,49 +1132,67 @@
       <c r="N3" s="6"/>
       <c r="O3" s="3"/>
       <c r="P3" s="7"/>
-      <c r="Q3" s="8">
-        <f>B3-E3-H3-K3-N3</f>
-        <v>11798</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="Q3" s="6"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="7"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="7"/>
+      <c r="W3" s="8">
+        <f>B3-E3-H3-K3-N3-Q3-T3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A4" s="30" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="20">
-        <v>37318</v>
+        <v>40793</v>
       </c>
       <c r="C4" s="21"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="4"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="4">
+        <v>17300</v>
+      </c>
       <c r="I4" s="2"/>
       <c r="J4" s="5"/>
-      <c r="K4" s="4"/>
+      <c r="K4" s="4">
+        <v>14500</v>
+      </c>
       <c r="L4" s="2"/>
       <c r="M4" s="5"/>
       <c r="N4" s="4"/>
       <c r="O4" s="2"/>
       <c r="P4" s="5"/>
-      <c r="Q4" s="8">
-        <f t="shared" ref="Q4:Q19" si="0">B4-E4-H4-K4-N4</f>
-        <v>37318</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q4" s="4">
+        <v>9000</v>
+      </c>
+      <c r="R4" s="2"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="4"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="5"/>
+      <c r="W4" s="8">
+        <f t="shared" ref="W4:W13" si="0">B4-E4-H4-K4-N4-Q4-T4</f>
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="25">
+      <c r="B5" s="22">
         <v>11560</v>
       </c>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="29"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="5"/>
       <c r="H5" s="4"/>
       <c r="I5" s="2"/>
       <c r="J5" s="5"/>
@@ -1143,47 +1202,61 @@
       <c r="N5" s="4"/>
       <c r="O5" s="2"/>
       <c r="P5" s="5"/>
-      <c r="Q5" s="8">
+      <c r="Q5" s="4"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="5"/>
+      <c r="T5" s="4"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="5"/>
+      <c r="W5" s="8">
         <f t="shared" si="0"/>
         <v>11560</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A6" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="25">
-        <v>14534</v>
-      </c>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="29"/>
+      <c r="B6" s="22">
+        <v>12972</v>
+      </c>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="5"/>
       <c r="H6" s="4"/>
       <c r="I6" s="2"/>
       <c r="J6" s="5"/>
       <c r="K6" s="4"/>
       <c r="L6" s="2"/>
       <c r="M6" s="5"/>
-      <c r="N6" s="4"/>
+      <c r="N6" s="4">
+        <v>12972</v>
+      </c>
       <c r="O6" s="2"/>
       <c r="P6" s="5"/>
-      <c r="Q6" s="8">
+      <c r="Q6" s="4"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="5"/>
+      <c r="T6" s="4"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="5"/>
+      <c r="W6" s="8">
         <f t="shared" si="0"/>
-        <v>14534</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="25"/>
-      <c r="C7" s="26"/>
-      <c r="D7" s="26"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="29"/>
+        <v>8</v>
+      </c>
+      <c r="B7" s="22"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="5"/>
       <c r="H7" s="4"/>
       <c r="I7" s="2"/>
       <c r="J7" s="5"/>
@@ -1193,21 +1266,27 @@
       <c r="N7" s="4"/>
       <c r="O7" s="2"/>
       <c r="P7" s="5"/>
-      <c r="Q7" s="8">
+      <c r="Q7" s="4"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="5"/>
+      <c r="T7" s="4"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="5"/>
+      <c r="W7" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" s="25"/>
-      <c r="C8" s="26"/>
-      <c r="D8" s="26"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="29"/>
+        <v>14</v>
+      </c>
+      <c r="B8" s="22"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="5"/>
       <c r="H8" s="4"/>
       <c r="I8" s="2"/>
       <c r="J8" s="5"/>
@@ -1217,21 +1296,27 @@
       <c r="N8" s="4"/>
       <c r="O8" s="2"/>
       <c r="P8" s="5"/>
-      <c r="Q8" s="8">
+      <c r="Q8" s="4"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="5"/>
+      <c r="T8" s="4"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="5"/>
+      <c r="W8" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="25"/>
-      <c r="C9" s="26"/>
-      <c r="D9" s="26"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="29"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="5"/>
       <c r="H9" s="4"/>
       <c r="I9" s="2"/>
       <c r="J9" s="5"/>
@@ -1241,21 +1326,27 @@
       <c r="N9" s="4"/>
       <c r="O9" s="2"/>
       <c r="P9" s="5"/>
-      <c r="Q9" s="8">
+      <c r="Q9" s="4"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="5"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="5"/>
+      <c r="W9" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="30"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="34"/>
+        <v>22</v>
+      </c>
+      <c r="B10" s="24"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="11"/>
       <c r="H10" s="9"/>
       <c r="I10" s="10"/>
       <c r="J10" s="11"/>
@@ -1265,21 +1356,27 @@
       <c r="N10" s="9"/>
       <c r="O10" s="10"/>
       <c r="P10" s="11"/>
-      <c r="Q10" s="8">
+      <c r="Q10" s="9"/>
+      <c r="R10" s="10"/>
+      <c r="S10" s="11"/>
+      <c r="T10" s="9"/>
+      <c r="U10" s="10"/>
+      <c r="V10" s="11"/>
+      <c r="W10" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="30"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="34"/>
+        <v>13</v>
+      </c>
+      <c r="B11" s="24"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="11"/>
       <c r="H11" s="9"/>
       <c r="I11" s="10"/>
       <c r="J11" s="11"/>
@@ -1289,21 +1386,27 @@
       <c r="N11" s="9"/>
       <c r="O11" s="10"/>
       <c r="P11" s="11"/>
-      <c r="Q11" s="8">
+      <c r="Q11" s="9"/>
+      <c r="R11" s="10"/>
+      <c r="S11" s="11"/>
+      <c r="T11" s="9"/>
+      <c r="U11" s="10"/>
+      <c r="V11" s="11"/>
+      <c r="W11" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="30"/>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="34"/>
+        <v>25</v>
+      </c>
+      <c r="B12" s="24"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="11"/>
       <c r="H12" s="9"/>
       <c r="I12" s="10"/>
       <c r="J12" s="11"/>
@@ -1313,21 +1416,33 @@
       <c r="N12" s="9"/>
       <c r="O12" s="10"/>
       <c r="P12" s="11"/>
-      <c r="Q12" s="8">
+      <c r="Q12" s="9"/>
+      <c r="R12" s="10"/>
+      <c r="S12" s="11"/>
+      <c r="T12" s="9"/>
+      <c r="U12" s="10"/>
+      <c r="V12" s="11"/>
+      <c r="W12" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="B13" s="30"/>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="34"/>
+    <row r="13" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="31" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="24">
+        <v>7599</v>
+      </c>
+      <c r="C13" s="25">
+        <v>8432</v>
+      </c>
+      <c r="D13" s="25">
+        <v>14</v>
+      </c>
+      <c r="E13" s="9"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="11"/>
       <c r="H13" s="9"/>
       <c r="I13" s="10"/>
       <c r="J13" s="11"/>
@@ -1337,21 +1452,33 @@
       <c r="N13" s="9"/>
       <c r="O13" s="10"/>
       <c r="P13" s="11"/>
-      <c r="Q13" s="8">
+      <c r="Q13" s="9">
+        <v>7599</v>
+      </c>
+      <c r="R13" s="10">
+        <v>8432</v>
+      </c>
+      <c r="S13" s="11">
+        <v>14</v>
+      </c>
+      <c r="T13" s="9"/>
+      <c r="U13" s="10"/>
+      <c r="V13" s="11"/>
+      <c r="W13" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="30"/>
-      <c r="C14" s="31"/>
-      <c r="D14" s="31"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="33"/>
-      <c r="G14" s="34"/>
+        <v>17</v>
+      </c>
+      <c r="B14" s="24"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="9"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="11"/>
       <c r="H14" s="9"/>
       <c r="I14" s="10"/>
       <c r="J14" s="11"/>
@@ -1361,21 +1488,27 @@
       <c r="N14" s="9"/>
       <c r="O14" s="10"/>
       <c r="P14" s="11"/>
-      <c r="Q14" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Q14" s="9"/>
+      <c r="R14" s="10"/>
+      <c r="S14" s="11"/>
+      <c r="T14" s="9"/>
+      <c r="U14" s="10"/>
+      <c r="V14" s="11"/>
+      <c r="W14" s="8">
+        <f>B14-E14-H14-K14-T14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="25"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="29"/>
+        <v>18</v>
+      </c>
+      <c r="B15" s="22"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="5"/>
       <c r="H15" s="4"/>
       <c r="I15" s="2"/>
       <c r="J15" s="5"/>
@@ -1385,21 +1518,27 @@
       <c r="N15" s="9"/>
       <c r="O15" s="10"/>
       <c r="P15" s="11"/>
-      <c r="Q15" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Q15" s="9"/>
+      <c r="R15" s="10"/>
+      <c r="S15" s="11"/>
+      <c r="T15" s="9"/>
+      <c r="U15" s="10"/>
+      <c r="V15" s="11"/>
+      <c r="W15" s="8">
+        <f>B15-E15-H15-K15-T15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B16" s="30"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="34"/>
+        <v>9</v>
+      </c>
+      <c r="B16" s="24"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="11"/>
       <c r="H16" s="9"/>
       <c r="I16" s="10"/>
       <c r="J16" s="11"/>
@@ -1409,21 +1548,27 @@
       <c r="N16" s="9"/>
       <c r="O16" s="10"/>
       <c r="P16" s="11"/>
-      <c r="Q16" s="8">
-        <f t="shared" ref="Q16:Q18" si="1">B16-E16-H16-K16-N16</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+      <c r="Q16" s="9"/>
+      <c r="R16" s="10"/>
+      <c r="S16" s="11"/>
+      <c r="T16" s="9"/>
+      <c r="U16" s="10"/>
+      <c r="V16" s="11"/>
+      <c r="W16" s="8">
+        <f t="shared" ref="W16:W18" si="1">B16-E16-H16-K16-T16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="30"/>
-      <c r="C17" s="31"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="34"/>
+        <v>15</v>
+      </c>
+      <c r="B17" s="24"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="11"/>
       <c r="H17" s="9"/>
       <c r="I17" s="10"/>
       <c r="J17" s="11"/>
@@ -1433,21 +1578,27 @@
       <c r="N17" s="9"/>
       <c r="O17" s="10"/>
       <c r="P17" s="11"/>
-      <c r="Q17" s="8">
+      <c r="Q17" s="9"/>
+      <c r="R17" s="10"/>
+      <c r="S17" s="11"/>
+      <c r="T17" s="9"/>
+      <c r="U17" s="10"/>
+      <c r="V17" s="11"/>
+      <c r="W17" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:17" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="30"/>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="34"/>
+        <v>24</v>
+      </c>
+      <c r="B18" s="24"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="11"/>
       <c r="H18" s="9"/>
       <c r="I18" s="10"/>
       <c r="J18" s="11"/>
@@ -1457,21 +1608,27 @@
       <c r="N18" s="9"/>
       <c r="O18" s="10"/>
       <c r="P18" s="11"/>
-      <c r="Q18" s="8">
+      <c r="Q18" s="9"/>
+      <c r="R18" s="10"/>
+      <c r="S18" s="11"/>
+      <c r="T18" s="9"/>
+      <c r="U18" s="10"/>
+      <c r="V18" s="11"/>
+      <c r="W18" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:23" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="30"/>
-      <c r="C19" s="31"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="27"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="34"/>
+        <v>23</v>
+      </c>
+      <c r="B19" s="24"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="11"/>
       <c r="H19" s="9"/>
       <c r="I19" s="10"/>
       <c r="J19" s="11"/>
@@ -1481,30 +1638,36 @@
       <c r="N19" s="9"/>
       <c r="O19" s="10"/>
       <c r="P19" s="11"/>
-      <c r="Q19" s="8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" s="36">
-        <f t="shared" ref="B20:M20" si="2">SUM(B3:B19)</f>
-        <v>75210</v>
+      <c r="Q19" s="9"/>
+      <c r="R19" s="10"/>
+      <c r="S19" s="11"/>
+      <c r="T19" s="9"/>
+      <c r="U19" s="10"/>
+      <c r="V19" s="11"/>
+      <c r="W19" s="8">
+        <f>B19-E19-H19-K19-T19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="26">
+        <f t="shared" ref="B20:S20" si="2">SUM(B3:B19)</f>
+        <v>87400</v>
       </c>
       <c r="C20" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>8432</v>
       </c>
       <c r="D20" s="13">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E20" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>14476</v>
       </c>
       <c r="F20" s="14">
         <f t="shared" si="2"/>
@@ -1516,7 +1679,7 @@
       </c>
       <c r="H20" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>17300</v>
       </c>
       <c r="I20" s="14">
         <f t="shared" si="2"/>
@@ -1528,7 +1691,7 @@
       </c>
       <c r="K20" s="12">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>14500</v>
       </c>
       <c r="L20" s="14">
         <f t="shared" si="2"/>
@@ -1539,25 +1702,49 @@
         <v>0</v>
       </c>
       <c r="N20" s="12">
-        <f t="shared" ref="N20:P20" si="3">SUM(N3:N19)</f>
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>12972</v>
       </c>
       <c r="O20" s="14">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P20" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="Q20" s="12">
+        <f t="shared" si="2"/>
+        <v>16599</v>
+      </c>
+      <c r="R20" s="14">
+        <f t="shared" si="2"/>
+        <v>8432</v>
+      </c>
+      <c r="S20" s="15">
+        <f t="shared" si="2"/>
+        <v>14</v>
+      </c>
+      <c r="T20" s="12">
+        <f t="shared" ref="T20:V20" si="3">SUM(T3:T19)</f>
+        <v>0</v>
+      </c>
+      <c r="U20" s="14">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="P20" s="15">
+      <c r="V20" s="15">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q20" s="16">
-        <f>SUM(Q3:Q19)</f>
-        <v>75210</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A21" s="35" t="s">
-        <v>30</v>
+      <c r="W20" s="16">
+        <f>SUM(W3:W19)</f>
+        <v>11553</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A21" s="32" t="s">
+        <v>26</v>
       </c>
       <c r="B21">
         <f>1200+250</f>
@@ -1566,10 +1753,16 @@
       <c r="D21">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A22" s="35" t="s">
-        <v>31</v>
+      <c r="K21">
+        <v>1450</v>
+      </c>
+      <c r="M21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A22" s="29" t="s">
+        <v>27</v>
       </c>
       <c r="B22">
         <f>800+174</f>
@@ -1578,10 +1771,16 @@
       <c r="D22">
         <v>2</v>
       </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A23" s="35" t="s">
-        <v>32</v>
+      <c r="N22">
+        <v>974</v>
+      </c>
+      <c r="P22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>28</v>
       </c>
       <c r="B23">
         <f>1000+252</f>
@@ -1590,18 +1789,136 @@
       <c r="D23">
         <v>3</v>
       </c>
+      <c r="E23">
+        <v>1252</v>
+      </c>
+      <c r="G23">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="29" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24">
+        <v>1084</v>
+      </c>
+      <c r="D24">
+        <v>4</v>
+      </c>
+      <c r="N24">
+        <v>1084</v>
+      </c>
+      <c r="P24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" s="1" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="26">
+        <f>SUM(B20:B24)</f>
+        <v>92160</v>
+      </c>
+      <c r="C25" s="13">
+        <f>SUM(C20:C24)</f>
+        <v>8432</v>
+      </c>
+      <c r="D25" s="13">
+        <f>SUM(D20:D24)</f>
+        <v>26</v>
+      </c>
+      <c r="E25" s="12">
+        <f>SUM(E20:E24)</f>
+        <v>15728</v>
+      </c>
+      <c r="F25" s="14">
+        <f>SUM(F20:F24)</f>
+        <v>0</v>
+      </c>
+      <c r="G25" s="15">
+        <f>SUM(G20:G24)</f>
+        <v>3</v>
+      </c>
+      <c r="H25" s="12">
+        <f>SUM(H20:H24)</f>
+        <v>17300</v>
+      </c>
+      <c r="I25" s="14">
+        <f>SUM(I20:I24)</f>
+        <v>0</v>
+      </c>
+      <c r="J25" s="15">
+        <f>SUM(J20:J24)</f>
+        <v>0</v>
+      </c>
+      <c r="K25" s="12">
+        <f>SUM(K20:K24)</f>
+        <v>15950</v>
+      </c>
+      <c r="L25" s="14">
+        <f>SUM(L20:L24)</f>
+        <v>0</v>
+      </c>
+      <c r="M25" s="15">
+        <f>SUM(M20:M24)</f>
+        <v>3</v>
+      </c>
+      <c r="N25" s="12">
+        <f>SUM(N20:N24)</f>
+        <v>15030</v>
+      </c>
+      <c r="O25" s="14">
+        <f>SUM(O20:O24)</f>
+        <v>0</v>
+      </c>
+      <c r="P25" s="15">
+        <f>SUM(P20:P24)</f>
+        <v>6</v>
+      </c>
+      <c r="Q25" s="12">
+        <f>SUM(Q20:Q24)</f>
+        <v>16599</v>
+      </c>
+      <c r="R25" s="14">
+        <f>SUM(R20:R24)</f>
+        <v>8432</v>
+      </c>
+      <c r="S25" s="15">
+        <f>SUM(S20:S24)</f>
+        <v>14</v>
+      </c>
+      <c r="T25" s="12">
+        <f>SUM(T20:T24)</f>
+        <v>0</v>
+      </c>
+      <c r="U25" s="14">
+        <f>SUM(U20:U24)</f>
+        <v>0</v>
+      </c>
+      <c r="V25" s="15">
+        <f>SUM(V20:V24)</f>
+        <v>0</v>
+      </c>
+      <c r="W25" s="16">
+        <f>SUM(W20:W24)</f>
+        <v>11553</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="Q1:Q2"/>
+  <mergeCells count="11">
+    <mergeCell ref="W1:W2"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="E1:G1"/>
     <mergeCell ref="H1:J1"/>
     <mergeCell ref="K1:M1"/>
-    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="T1:V1"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:D2"/>
+    <mergeCell ref="N1:P1"/>
+    <mergeCell ref="Q1:S1"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
